--- a/src/test/resources/testdata/MultiBankTestData.xlsx
+++ b/src/test/resources/testdata/MultiBankTestData.xlsx
@@ -3357,12 +3357,12 @@
       </c>
       <c r="F24" s="41" t="inlineStr">
         <is>
-          <t>verifySpotMarketContentLoadsWithinTimeout</t>
+          <t>verifySpotMarketSectionRenders</t>
         </is>
       </c>
       <c r="G24" s="41" t="inlineStr">
         <is>
-          <t>timeoutSeconds=20;expectedHeading=Spot market</t>
+          <t>expectedText=Spot market</t>
         </is>
       </c>
       <c r="H24" s="41" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>verifySpotMarketContentLoadsWithinTimeout</t>
+          <t>verifySpotMarketSectionRenders</t>
         </is>
       </c>
       <c r="G22" s="41" t="inlineStr">
         <is>
-          <t>timeoutSeconds=25;expectedHeading=Spot market</t>
+          <t>expectedText=Spot market</t>
         </is>
       </c>
       <c r="H22" s="41" t="inlineStr">

--- a/src/test/resources/testdata/MultiBankTestData.xlsx
+++ b/src/test/resources/testdata/MultiBankTestData.xlsx
@@ -3884,12 +3884,12 @@
       </c>
       <c r="G33" s="47" t="inlineStr">
         <is>
-          <t>links=Explore:/explore|Features:/features|Company:/company|Support:/support|Download the app:mbio.go.link;expectedStatusMax=399</t>
+          <t>links=Explore all assets:/explore|View platform features:https://trade.mb.io/login|Start Portfolio:https://trade.mb.io/register;expectedStatusMax=399</t>
         </is>
       </c>
       <c r="H33" s="47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I33" s="47" t="inlineStr">

--- a/src/test/resources/testdata/MultiBankTestData.xlsx
+++ b/src/test/resources/testdata/MultiBankTestData.xlsx
@@ -2111,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -3647,14 +3647,10 @@
       </c>
       <c r="F29" s="44" t="inlineStr">
         <is>
-          <t>verifyFooterPolicyLinkDestination</t>
-        </is>
-      </c>
-      <c r="G29" s="44" t="inlineStr">
-        <is>
-          <t>linkText=Privacy Policy;expectedPath=/about/privacy-policy-gcc;target=_self</t>
-        </is>
-      </c>
+          <t>verifyAllFooterLinksResolve</t>
+        </is>
+      </c>
+      <c r="G29" s="44" t="inlineStr"/>
       <c r="H29" s="44" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3680,37 +3676,37 @@
     <row r="30" ht="54" customHeight="1" s="50">
       <c r="A30" s="40" t="inlineStr">
         <is>
-          <t>MBQA-141</t>
+          <t>MBQA-151</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>DWEB_FTR_002</t>
+          <t>DWEB_ERR_001</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>Content &amp; Links</t>
+          <t>Negative / Edge Cases</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>Common Footer</t>
+          <t>Error Page</t>
         </is>
       </c>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>FooterLinkTests</t>
+          <t>ErrorPageInvalidRouteTests</t>
         </is>
       </c>
       <c r="F30" s="41" t="inlineStr">
         <is>
-          <t>verifyFooterPolicyLinkDestination</t>
+          <t>verifyInvalidRouteDisplaysPageNotFound</t>
         </is>
       </c>
       <c r="G30" s="41" t="inlineStr">
         <is>
-          <t>linkText=Cookie Policy;expectedPath=/about/cookie-policy-gcc;target=_self</t>
+          <t>invalidPath=/non-existing-route-for-automation-check;expectedHeading=Page not found;expectedText=Back to Homepage</t>
         </is>
       </c>
       <c r="H30" s="41" t="inlineStr">
@@ -3720,213 +3716,99 @@
       </c>
       <c r="I30" s="41" t="inlineStr">
         <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="J30" s="41" t="inlineStr">
+        <is>
+          <t>Invalid route displays page not found</t>
+        </is>
+      </c>
+      <c r="K30" s="42" t="inlineStr">
+        <is>
+          <t>Negative route handling</t>
+        </is>
+      </c>
+      <c r="L30" s="39" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1" s="50">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>MBQA-152</t>
+        </is>
+      </c>
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>DWEB_LNK_001</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>Negative / Edge Cases</t>
+        </is>
+      </c>
+      <c r="D31" s="47" t="inlineStr">
+        <is>
+          <t>Common Links</t>
+        </is>
+      </c>
+      <c r="E31" s="47" t="inlineStr">
+        <is>
+          <t>BrokenLinkTests</t>
+        </is>
+      </c>
+      <c r="F31" s="47" t="inlineStr">
+        <is>
+          <t>verifyCriticalLinksAreNotBroken</t>
+        </is>
+      </c>
+      <c r="G31" s="47" t="inlineStr">
+        <is>
+          <t>links=Explore all assets:/explore|View platform features:https://trade.mb.io/login|Start Portfolio:https://trade.mb.io/register;expectedStatusMax=399</t>
+        </is>
+      </c>
+      <c r="H31" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I31" s="47" t="inlineStr">
+        <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="J30" s="41" t="inlineStr">
-        <is>
-          <t>Cookie Policy footer link is available</t>
-        </is>
-      </c>
-      <c r="K30" s="42" t="inlineStr">
-        <is>
-          <t>Reusable footer component</t>
-        </is>
-      </c>
-      <c r="L30" s="39" t="n"/>
-    </row>
-    <row r="31" ht="54" customHeight="1" s="50">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>MBQA-141</t>
-        </is>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>DWEB_FTR_003</t>
-        </is>
-      </c>
-      <c r="C31" s="44" t="inlineStr">
-        <is>
-          <t>Content &amp; Links</t>
-        </is>
-      </c>
-      <c r="D31" s="44" t="inlineStr">
-        <is>
-          <t>Common Footer</t>
-        </is>
-      </c>
-      <c r="E31" s="44" t="inlineStr">
-        <is>
-          <t>FooterLinkTests</t>
-        </is>
-      </c>
-      <c r="F31" s="44" t="inlineStr">
-        <is>
-          <t>verifyFooterPolicyLinkDestination</t>
-        </is>
-      </c>
-      <c r="G31" s="44" t="inlineStr">
-        <is>
-          <t>linkText=Terms &amp; Conditions;expectedPath=/about/terms-conditions-gcc;target=_self</t>
-        </is>
-      </c>
-      <c r="H31" s="44" t="inlineStr">
+      <c r="J31" s="47" t="inlineStr">
+        <is>
+          <t>Critical navigation and CTA links are not broken</t>
+        </is>
+      </c>
+      <c r="K31" s="48" t="inlineStr">
+        <is>
+          <t>Use HEAD, fallback GET if server blocks HEAD</t>
+        </is>
+      </c>
+      <c r="L31" s="39" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1" s="50">
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I31" s="44" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="J31" s="44" t="inlineStr">
-        <is>
-          <t>Terms and Conditions footer link is available</t>
-        </is>
-      </c>
-      <c r="K31" s="45" t="inlineStr">
-        <is>
-          <t>Reusable footer component</t>
-        </is>
-      </c>
-      <c r="L31" s="39" t="n"/>
-    </row>
-    <row r="32" ht="54" customHeight="1" s="50">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>MBQA-151</t>
-        </is>
-      </c>
-      <c r="B32" s="41" t="inlineStr">
-        <is>
-          <t>DWEB_ERR_001</t>
-        </is>
-      </c>
-      <c r="C32" s="41" t="inlineStr">
-        <is>
-          <t>Negative / Edge Cases</t>
-        </is>
-      </c>
-      <c r="D32" s="41" t="inlineStr">
-        <is>
-          <t>Error Page</t>
-        </is>
-      </c>
-      <c r="E32" s="41" t="inlineStr">
-        <is>
-          <t>ErrorPageInvalidRouteTests</t>
-        </is>
-      </c>
-      <c r="F32" s="41" t="inlineStr">
-        <is>
-          <t>verifyInvalidRouteDisplaysPageNotFound</t>
-        </is>
-      </c>
-      <c r="G32" s="41" t="inlineStr">
-        <is>
-          <t>invalidPath=/non-existing-route-for-automation-check;expectedHeading=Page not found;expectedText=Back to Homepage</t>
-        </is>
-      </c>
-      <c r="H32" s="41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I32" s="41" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="J32" s="41" t="inlineStr">
-        <is>
-          <t>Invalid route displays page not found</t>
-        </is>
-      </c>
-      <c r="K32" s="42" t="inlineStr">
-        <is>
-          <t>Negative route handling</t>
-        </is>
-      </c>
-      <c r="L32" s="39" t="n"/>
-    </row>
-    <row r="33" ht="54" customHeight="1" s="50">
-      <c r="A33" s="46" t="inlineStr">
-        <is>
-          <t>MBQA-152</t>
-        </is>
-      </c>
-      <c r="B33" s="47" t="inlineStr">
-        <is>
-          <t>DWEB_LNK_001</t>
-        </is>
-      </c>
-      <c r="C33" s="47" t="inlineStr">
-        <is>
-          <t>Negative / Edge Cases</t>
-        </is>
-      </c>
-      <c r="D33" s="47" t="inlineStr">
-        <is>
-          <t>Common Links</t>
-        </is>
-      </c>
-      <c r="E33" s="47" t="inlineStr">
-        <is>
-          <t>BrokenLinkTests</t>
-        </is>
-      </c>
-      <c r="F33" s="47" t="inlineStr">
-        <is>
-          <t>verifyCriticalLinksAreNotBroken</t>
-        </is>
-      </c>
-      <c r="G33" s="47" t="inlineStr">
-        <is>
-          <t>links=Explore all assets:/explore|View platform features:https://trade.mb.io/login|Start Portfolio:https://trade.mb.io/register;expectedStatusMax=399</t>
-        </is>
-      </c>
-      <c r="H33" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I33" s="47" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="J33" s="47" t="inlineStr">
-        <is>
-          <t>Critical navigation and CTA links are not broken</t>
-        </is>
-      </c>
-      <c r="K33" s="48" t="inlineStr">
-        <is>
-          <t>Use HEAD, fallback GET if server blocks HEAD</t>
-        </is>
-      </c>
-      <c r="L33" s="39" t="n"/>
-    </row>
-    <row r="34" ht="13.55" customHeight="1" s="50">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="27" t="n"/>
-    </row>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="27" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1" s="50"/>
+    <row r="34" ht="13.55" customHeight="1" s="50"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
@@ -3959,7 +3841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="49" min="1" max="1"/>
@@ -5296,37 +5178,37 @@
     <row r="26" ht="54" customHeight="1" s="50">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>MBQA-241</t>
+          <t>MBQA-251</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>MWEB_FTR_001</t>
+          <t>MWEB_ERR_001</t>
         </is>
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>Content &amp; Links</t>
+          <t>Negative / Edge Cases</t>
         </is>
       </c>
       <c r="D26" s="41" t="inlineStr">
         <is>
-          <t>Common Footer</t>
+          <t>Error Page</t>
         </is>
       </c>
       <c r="E26" s="41" t="inlineStr">
         <is>
-          <t>FooterLinkTests</t>
+          <t>ErrorPageInvalidRouteTests</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
         <is>
-          <t>verifyFooterPolicyLinkDestination</t>
+          <t>verifyInvalidRouteDisplaysPageNotFound</t>
         </is>
       </c>
       <c r="G26" s="41" t="inlineStr">
         <is>
-          <t>linkText=Privacy Policy;expectedPath=/about/privacy-policy-gcc;target=_self</t>
+          <t>invalidPath=/non-existing-route-for-automation-check;expectedHeading=Page not found;expectedText=Back to Homepage</t>
         </is>
       </c>
       <c r="H26" s="41" t="inlineStr">
@@ -5336,209 +5218,95 @@
       </c>
       <c r="I26" s="41" t="inlineStr">
         <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="J26" s="41" t="inlineStr">
+        <is>
+          <t>Invalid route displays mobile page not found</t>
+        </is>
+      </c>
+      <c r="K26" s="42" t="inlineStr">
+        <is>
+          <t>Negative route handling</t>
+        </is>
+      </c>
+      <c r="L26" s="39" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1" s="50">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>MBQA-252</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>MWEB_LNK_001</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>Negative / Edge Cases</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>Common Links</t>
+        </is>
+      </c>
+      <c r="E27" s="47" t="inlineStr">
+        <is>
+          <t>BrokenLinkTests</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>verifyCriticalLinksAreNotBroken</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="inlineStr">
+        <is>
+          <t>links=Explore:/explore|Features:/features|Company:/company|Support:/support|Download the app:mbio.go.link;expectedStatusMax=399</t>
+        </is>
+      </c>
+      <c r="H27" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="47" t="inlineStr">
+        <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="J26" s="41" t="inlineStr">
-        <is>
-          <t>Privacy Policy footer link is available on mobile</t>
-        </is>
-      </c>
-      <c r="K26" s="42" t="inlineStr">
-        <is>
-          <t>Footer may require scrolling</t>
-        </is>
-      </c>
-      <c r="L26" s="39" t="n"/>
-    </row>
-    <row r="27" ht="54" customHeight="1" s="50">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>MBQA-241</t>
-        </is>
-      </c>
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>MWEB_FTR_002</t>
-        </is>
-      </c>
-      <c r="C27" s="44" t="inlineStr">
-        <is>
-          <t>Content &amp; Links</t>
-        </is>
-      </c>
-      <c r="D27" s="44" t="inlineStr">
-        <is>
-          <t>Common Footer</t>
-        </is>
-      </c>
-      <c r="E27" s="44" t="inlineStr">
-        <is>
-          <t>FooterLinkTests</t>
-        </is>
-      </c>
-      <c r="F27" s="44" t="inlineStr">
-        <is>
-          <t>verifyFooterPolicyLinkDestination</t>
-        </is>
-      </c>
-      <c r="G27" s="44" t="inlineStr">
-        <is>
-          <t>linkText=Terms &amp; Conditions;expectedPath=/about/terms-conditions-gcc;target=_self</t>
-        </is>
-      </c>
-      <c r="H27" s="44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I27" s="44" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="J27" s="44" t="inlineStr">
-        <is>
-          <t>Terms and Conditions footer link is available on mobile</t>
-        </is>
-      </c>
-      <c r="K27" s="45" t="inlineStr">
-        <is>
-          <t>Footer may require scrolling</t>
+      <c r="J27" s="47" t="inlineStr">
+        <is>
+          <t>Critical mobile navigation and CTA links are not broken</t>
+        </is>
+      </c>
+      <c r="K27" s="48" t="inlineStr">
+        <is>
+          <t>Use HEAD, fallback GET if server blocks HEAD</t>
         </is>
       </c>
       <c r="L27" s="39" t="n"/>
     </row>
     <row r="28" ht="54" customHeight="1" s="50">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>MBQA-251</t>
-        </is>
-      </c>
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>MWEB_ERR_001</t>
-        </is>
-      </c>
-      <c r="C28" s="41" t="inlineStr">
-        <is>
-          <t>Negative / Edge Cases</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>Error Page</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="inlineStr">
-        <is>
-          <t>ErrorPageInvalidRouteTests</t>
-        </is>
-      </c>
-      <c r="F28" s="41" t="inlineStr">
-        <is>
-          <t>verifyInvalidRouteDisplaysPageNotFound</t>
-        </is>
-      </c>
-      <c r="G28" s="41" t="inlineStr">
-        <is>
-          <t>invalidPath=/non-existing-route-for-automation-check;expectedHeading=Page not found;expectedText=Back to Homepage</t>
-        </is>
-      </c>
-      <c r="H28" s="41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I28" s="41" t="inlineStr">
-        <is>
-          <t>Smoke</t>
-        </is>
-      </c>
-      <c r="J28" s="41" t="inlineStr">
-        <is>
-          <t>Invalid route displays mobile page not found</t>
-        </is>
-      </c>
-      <c r="K28" s="42" t="inlineStr">
-        <is>
-          <t>Negative route handling</t>
-        </is>
-      </c>
-      <c r="L28" s="39" t="n"/>
-    </row>
-    <row r="29" ht="54" customHeight="1" s="50">
-      <c r="A29" s="46" t="inlineStr">
-        <is>
-          <t>MBQA-252</t>
-        </is>
-      </c>
-      <c r="B29" s="47" t="inlineStr">
-        <is>
-          <t>MWEB_LNK_001</t>
-        </is>
-      </c>
-      <c r="C29" s="47" t="inlineStr">
-        <is>
-          <t>Negative / Edge Cases</t>
-        </is>
-      </c>
-      <c r="D29" s="47" t="inlineStr">
-        <is>
-          <t>Common Links</t>
-        </is>
-      </c>
-      <c r="E29" s="47" t="inlineStr">
-        <is>
-          <t>BrokenLinkTests</t>
-        </is>
-      </c>
-      <c r="F29" s="47" t="inlineStr">
-        <is>
-          <t>verifyCriticalLinksAreNotBroken</t>
-        </is>
-      </c>
-      <c r="G29" s="47" t="inlineStr">
-        <is>
-          <t>links=Explore:/explore|Features:/features|Company:/company|Support:/support|Download the app:mbio.go.link;expectedStatusMax=399</t>
-        </is>
-      </c>
-      <c r="H29" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I29" s="47" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="J29" s="47" t="inlineStr">
-        <is>
-          <t>Critical mobile navigation and CTA links are not broken</t>
-        </is>
-      </c>
-      <c r="K29" s="48" t="inlineStr">
-        <is>
-          <t>Use HEAD, fallback GET if server blocks HEAD</t>
-        </is>
-      </c>
-      <c r="L29" s="39" t="n"/>
-    </row>
-    <row r="30" ht="13.55" customHeight="1" s="50">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="27" t="n"/>
-    </row>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="27" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1" s="50"/>
+    <row r="30" ht="13.55" customHeight="1" s="50"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
